--- a/results/05-2025/beta/contributions-05-2025.xlsx
+++ b/results/05-2025/beta/contributions-05-2025.xlsx
@@ -22075,7 +22075,7 @@
         <v>0.0203237932082108</v>
       </c>
       <c r="F221" t="n">
-        <v>0.352356703711459</v>
+        <v>0.320772153219421</v>
       </c>
       <c r="G221" t="n">
         <v>-0.0138441171093988</v>
@@ -22138,19 +22138,19 @@
         <v>0.0519650820145759</v>
       </c>
       <c r="AA221" t="n">
-        <v>0.173285721695267</v>
+        <v>0.141642232637264</v>
       </c>
       <c r="AB221" t="n">
         <v>0.0792824983544705</v>
       </c>
       <c r="AC221" t="n">
-        <v>0.25242563744184</v>
+        <v>0.220808191599737</v>
       </c>
       <c r="AD221" t="n">
-        <v>0.38331070976576</v>
+        <v>0.351693263923657</v>
       </c>
       <c r="AE221" t="n">
-        <v>0.249911053898</v>
+        <v>0.242006692437474</v>
       </c>
     </row>
     <row r="222">
@@ -22161,91 +22161,91 @@
         <v>32</v>
       </c>
       <c r="C222" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D222" t="n">
-        <v>-0.478539620704419</v>
+        <v>-0.448410944343367</v>
       </c>
       <c r="E222" t="n">
-        <v>-0.155854506418624</v>
+        <v>-0.0555228167079438</v>
       </c>
       <c r="F222" t="n">
-        <v>0.0561496195149544</v>
+        <v>0.000887694194888976</v>
       </c>
       <c r="G222" t="n">
-        <v>0.0336434229614811</v>
+        <v>0.0230168775746161</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.0335374701692082</v>
+        <v>-0.0237766819437887</v>
       </c>
       <c r="I222" t="n">
-        <v>0.0247701402395646</v>
+        <v>0.0247624002205425</v>
       </c>
       <c r="J222" t="n">
-        <v>0.0185477177255184</v>
+        <v>0.0130898387137104</v>
       </c>
       <c r="K222" t="n">
-        <v>0.0315201952467115</v>
+        <v>0.0889163988424009</v>
       </c>
       <c r="L222" t="n">
-        <v>-0.00938209845407849</v>
+        <v>-0.00903351799913496</v>
       </c>
       <c r="M222" t="n">
         <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>-0.0982502827494242</v>
+        <v>-0.0977555461765783</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
       </c>
       <c r="P222" t="n">
-        <v>-0.00179426720960946</v>
+        <v>-0.00173568861995069</v>
       </c>
       <c r="Q222" t="n">
-        <v>-0.0745431130409719</v>
+        <v>-0.0740815925257514</v>
       </c>
       <c r="R222" t="n">
-        <v>-0.0285313008514029</v>
+        <v>-0.0283836090183389</v>
       </c>
       <c r="S222" t="n">
-        <v>-0.0152057691917747</v>
+        <v>-0.0151216627905268</v>
       </c>
       <c r="T222" t="n">
-        <v>-0.0107776193133762</v>
+        <v>-0.0107185725875838</v>
       </c>
       <c r="U222" t="n">
-        <v>-0.0305402645619535</v>
+        <v>-0.0303836095223133</v>
       </c>
       <c r="V222" t="n">
-        <v>-0.000308588781147387</v>
+        <v>-0.000306472233792491</v>
       </c>
       <c r="W222" t="n">
-        <v>0.0937785525713203</v>
+        <v>0.0957467985807591</v>
       </c>
       <c r="X222" t="n">
-        <v>0.0523591267751843</v>
+        <v>0.0506366197789983</v>
       </c>
       <c r="Y222" t="n">
-        <v>-1.14671596533796</v>
+        <v>-1.11590811334155</v>
       </c>
       <c r="Z222" t="n">
-        <v>0.512321838214912</v>
+        <v>0.611974352290235</v>
       </c>
       <c r="AA222" t="n">
-        <v>0.0995549025252544</v>
+        <v>0.0379824261369196</v>
       </c>
       <c r="AB222" t="n">
-        <v>-0.0915630095087931</v>
+        <v>-0.0320323529213693</v>
       </c>
       <c r="AC222" t="n">
-        <v>0.00808702840803584</v>
+        <v>0.00596285302708463</v>
       </c>
       <c r="AD222" t="n">
-        <v>-0.626307098715008</v>
+        <v>-0.497970908024226</v>
       </c>
       <c r="AE222" t="n">
-        <v>0.0946329640882863</v>
+        <v>0.118812650300456</v>
       </c>
     </row>
     <row r="223">
@@ -22259,88 +22259,88 @@
         <v>0</v>
       </c>
       <c r="D223" t="n">
-        <v>-0.248975828230308</v>
+        <v>-0.249248818268166</v>
       </c>
       <c r="E223" t="n">
-        <v>-0.199385217122268</v>
+        <v>-0.199695743874746</v>
       </c>
       <c r="F223" t="n">
-        <v>-0.0377797147422318</v>
+        <v>-0.156013533678918</v>
       </c>
       <c r="G223" t="n">
-        <v>0.010139439382259</v>
+        <v>-0.0229096336459533</v>
       </c>
       <c r="H223" t="n">
-        <v>-0.0278661666290214</v>
+        <v>-0.0209670420243421</v>
       </c>
       <c r="I223" t="n">
-        <v>0.186189641255214</v>
+        <v>0.187447540148586</v>
       </c>
       <c r="J223" t="n">
-        <v>0.0103904193203431</v>
+        <v>0.00437836052720882</v>
       </c>
       <c r="K223" t="n">
-        <v>0.0246937868614803</v>
+        <v>0.111324982265797</v>
       </c>
       <c r="L223" t="n">
-        <v>0.0257227814290438</v>
+        <v>0.0290407251437075</v>
       </c>
       <c r="M223" t="n">
         <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>-0.0953834122569441</v>
+        <v>-0.0952674426342</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
       </c>
       <c r="P223" t="n">
-        <v>-0.00276396205753742</v>
+        <v>-0.00221816733340474</v>
       </c>
       <c r="Q223" t="n">
-        <v>-0.109062052921607</v>
+        <v>-0.108029532170016</v>
       </c>
       <c r="R223" t="n">
-        <v>-0.0269149109328438</v>
+        <v>-0.0268372083318616</v>
       </c>
       <c r="S223" t="n">
-        <v>-0.0136487494450995</v>
+        <v>-0.0135481346004777</v>
       </c>
       <c r="T223" t="n">
-        <v>-0.0101317313167497</v>
+        <v>-0.0100666538155058</v>
       </c>
       <c r="U223" t="n">
-        <v>-0.0238941629222095</v>
+        <v>-0.0238265827361572</v>
       </c>
       <c r="V223" t="n">
-        <v>-0.00152804714828666</v>
+        <v>-0.00152155122760946</v>
       </c>
       <c r="W223" t="n">
-        <v>0.140060467413595</v>
+        <v>0.284249157983166</v>
       </c>
       <c r="X223" t="n">
-        <v>-0.00950583007267417</v>
+        <v>0.0277154384918387</v>
       </c>
       <c r="Y223" t="n">
-        <v>-0.45162584336209</v>
+        <v>-0.451903423011569</v>
       </c>
       <c r="Z223" t="n">
-        <v>0.00326479800951387</v>
+        <v>0.00295886086865703</v>
       </c>
       <c r="AA223" t="n">
-        <v>0.141163440177305</v>
+        <v>-0.00774796042338479</v>
       </c>
       <c r="AB223" t="n">
-        <v>-0.102182602654285</v>
+        <v>0.171475055090399</v>
       </c>
       <c r="AC223" t="n">
-        <v>-0.960868350094338</v>
+        <v>-0.836258989634935</v>
       </c>
       <c r="AD223" t="n">
-        <v>-1.40922939544691</v>
+        <v>-1.28520355177785</v>
       </c>
       <c r="AE223" t="n">
-        <v>-0.287698433586331</v>
+        <v>-0.232512286456895</v>
       </c>
     </row>
     <row r="224">
@@ -22354,88 +22354,88 @@
         <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>-0.166532944876202</v>
+        <v>-0.166798809208384</v>
       </c>
       <c r="E224" t="n">
-        <v>-0.187936460235938</v>
+        <v>-0.188229156452396</v>
       </c>
       <c r="F224" t="n">
-        <v>0.00868966196835878</v>
+        <v>-0.0529121628143566</v>
       </c>
       <c r="G224" t="n">
-        <v>0.00174369233591945</v>
+        <v>-0.00227157348387961</v>
       </c>
       <c r="H224" t="n">
-        <v>-0.0438286610547766</v>
+        <v>-0.0337691213408335</v>
       </c>
       <c r="I224" t="n">
-        <v>0.185634234094115</v>
+        <v>0.185640134667603</v>
       </c>
       <c r="J224" t="n">
-        <v>0.0100903116066727</v>
+        <v>0.00531303485976639</v>
       </c>
       <c r="K224" t="n">
-        <v>0.0123084858560572</v>
+        <v>0.0643075441016236</v>
       </c>
       <c r="L224" t="n">
-        <v>0.00853026304516413</v>
+        <v>0.00853054699310905</v>
       </c>
       <c r="M224" t="n">
         <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>-0.000999644530239726</v>
+        <v>-0.000999677886176082</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
       </c>
       <c r="P224" t="n">
-        <v>-0.00416966743353797</v>
+        <v>-0.0041698066781528</v>
       </c>
       <c r="Q224" t="n">
-        <v>-0.0844761447994413</v>
+        <v>-0.084479023256342</v>
       </c>
       <c r="R224" t="n">
-        <v>-0.0261436824312532</v>
+        <v>-0.0261445603533861</v>
       </c>
       <c r="S224" t="n">
-        <v>-0.0137616939712075</v>
+        <v>-0.0137621546557025</v>
       </c>
       <c r="T224" t="n">
-        <v>-0.00851081712294958</v>
+        <v>-0.00851110165153467</v>
       </c>
       <c r="U224" t="n">
-        <v>0.000164903175940073</v>
+        <v>0.000164908676750042</v>
       </c>
       <c r="V224" t="n">
-        <v>-0.000451538070964669</v>
+        <v>-0.000451553135688187</v>
       </c>
       <c r="W224" t="n">
-        <v>0.128397199717318</v>
+        <v>0.244919300975177</v>
       </c>
       <c r="X224" t="n">
-        <v>0.0258860553695897</v>
+        <v>0.0581150227667486</v>
       </c>
       <c r="Y224" t="n">
-        <v>-0.219615983808899</v>
+        <v>-0.219883575094031</v>
       </c>
       <c r="Z224" t="n">
-        <v>-0.134853421303241</v>
+        <v>-0.13514439056675</v>
       </c>
       <c r="AA224" t="n">
-        <v>0.162382916651303</v>
+        <v>0.102147982814575</v>
       </c>
       <c r="AB224" t="n">
-        <v>0.0369005845804345</v>
+        <v>0.237620639396374</v>
       </c>
       <c r="AC224" t="n">
-        <v>-0.800779526319757</v>
+        <v>-0.66048715539827</v>
       </c>
       <c r="AD224" t="n">
-        <v>-1.1552489314319</v>
+        <v>-1.01551512105905</v>
       </c>
       <c r="AE224" t="n">
-        <v>-0.701868678957015</v>
+        <v>-0.611749079234367</v>
       </c>
     </row>
     <row r="225">
@@ -22449,88 +22449,88 @@
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>-0.164347961892139</v>
+        <v>-0.164610337971338</v>
       </c>
       <c r="E225" t="n">
-        <v>-0.186962810715843</v>
+        <v>-0.187253990549954</v>
       </c>
       <c r="F225" t="n">
-        <v>0.0305094767131727</v>
+        <v>-0.0115354271652405</v>
       </c>
       <c r="G225" t="n">
-        <v>-0.00867650055263411</v>
+        <v>-0.0126494837244951</v>
       </c>
       <c r="H225" t="n">
-        <v>-0.0400594342345965</v>
+        <v>-0.0302797568052593</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0729264876533954</v>
+        <v>0.0729288753077601</v>
       </c>
       <c r="J225" t="n">
-        <v>0.0109870396879908</v>
+        <v>0.00631494823857055</v>
       </c>
       <c r="K225" t="n">
-        <v>-0.0614438304167585</v>
+        <v>-0.0105258969706867</v>
       </c>
       <c r="L225" t="n">
-        <v>0.031462034132481</v>
+        <v>0.0314630752885804</v>
       </c>
       <c r="M225" t="n">
         <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>-0.000976441586203507</v>
+        <v>-0.000976474167753282</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
       </c>
       <c r="P225" t="n">
-        <v>-0.00489406526543916</v>
+        <v>-0.00489422873142007</v>
       </c>
       <c r="Q225" t="n">
-        <v>-0.0458627821010189</v>
+        <v>-0.0458643298889448</v>
       </c>
       <c r="R225" t="n">
-        <v>-0.0039170114040644</v>
+        <v>-0.00391714220318027</v>
       </c>
       <c r="S225" t="n">
-        <v>-0.0128853211981361</v>
+        <v>-0.0128857524521736</v>
       </c>
       <c r="T225" t="n">
-        <v>-0.00769182778612665</v>
+        <v>-0.00769208488228976</v>
       </c>
       <c r="U225" t="n">
-        <v>0.000120250077220826</v>
+        <v>0.000120254088549781</v>
       </c>
       <c r="V225" t="n">
-        <v>-0.000419008945748203</v>
+        <v>-0.000419022925064354</v>
       </c>
       <c r="W225" t="n">
-        <v>0.088325316126477</v>
+        <v>0.204030947507039</v>
       </c>
       <c r="X225" t="n">
-        <v>0.0499463991334815</v>
+        <v>0.081937230478174</v>
       </c>
       <c r="Y225" t="n">
-        <v>-0.269823373177304</v>
+        <v>-0.270088831467837</v>
       </c>
       <c r="Z225" t="n">
-        <v>-0.0814873994306788</v>
+        <v>-0.0817754970534545</v>
       </c>
       <c r="AA225" t="n">
-        <v>0.0657067308909287</v>
+        <v>0.0248105733395804</v>
       </c>
       <c r="AB225" t="n">
-        <v>0.0318501921225512</v>
+        <v>0.23036979774871</v>
       </c>
       <c r="AC225" t="n">
-        <v>-0.90246512564667</v>
+        <v>-0.7448799581137</v>
       </c>
       <c r="AD225" t="n">
-        <v>-1.25377589825465</v>
+        <v>-1.09674428663499</v>
       </c>
       <c r="AE225" t="n">
-        <v>-1.11114033096212</v>
+        <v>-0.973858466874029</v>
       </c>
     </row>
     <row r="226">
@@ -22544,88 +22544,88 @@
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>-0.146431268184141</v>
+        <v>-0.1466650408551</v>
       </c>
       <c r="E226" t="n">
-        <v>-0.185783913139997</v>
+        <v>-0.186073256934099</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.00707300234513214</v>
+        <v>-0.0189522313459746</v>
       </c>
       <c r="G226" t="n">
-        <v>-0.0140536776179016</v>
+        <v>-0.0179775359585874</v>
       </c>
       <c r="H226" t="n">
-        <v>-0.0255804119066301</v>
+        <v>-0.0160875170803828</v>
       </c>
       <c r="I226" t="n">
-        <v>0.31630420251704</v>
+        <v>0.316313900897622</v>
       </c>
       <c r="J226" t="n">
-        <v>0.00905729587482072</v>
+        <v>0.00448630901143698</v>
       </c>
       <c r="K226" t="n">
-        <v>-0.154248228369622</v>
+        <v>-0.145211356783697</v>
       </c>
       <c r="L226" t="n">
-        <v>0.0397754228515137</v>
+        <v>0.0397767362620755</v>
       </c>
       <c r="M226" t="n">
         <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>-0.000953840104076923</v>
+        <v>-0.000953871931338744</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
       </c>
       <c r="P226" t="n">
-        <v>-0.00450840000149874</v>
+        <v>-0.00450855057183472</v>
       </c>
       <c r="Q226" t="n">
-        <v>-0.0137009696744022</v>
+        <v>-0.0137014283278716</v>
       </c>
       <c r="R226" t="n">
-        <v>-0.00268335153568067</v>
+        <v>-0.00268344111187926</v>
       </c>
       <c r="S226" t="n">
-        <v>-0.0143784770951671</v>
+        <v>-0.0143789585117786</v>
       </c>
       <c r="T226" t="n">
-        <v>-0.00708149928860994</v>
+        <v>-0.00708173594971978</v>
       </c>
       <c r="U226" t="n">
-        <v>-0.000164650649922838</v>
+        <v>-0.000164656142851033</v>
       </c>
       <c r="V226" t="n">
-        <v>-0.000388262743740865</v>
+        <v>-0.000388275697211897</v>
       </c>
       <c r="W226" t="n">
-        <v>0.0946180945637056</v>
+        <v>0.209194869214311</v>
       </c>
       <c r="X226" t="n">
-        <v>-0.0164774463733194</v>
+        <v>0.0172211598615993</v>
       </c>
       <c r="Y226" t="n">
-        <v>-0.198923692698</v>
+        <v>-0.199159172197548</v>
       </c>
       <c r="Z226" t="n">
-        <v>-0.133291488626138</v>
+        <v>-0.133579125591651</v>
       </c>
       <c r="AA226" t="n">
-        <v>0.2787780994014</v>
+        <v>0.267938213323302</v>
       </c>
       <c r="AB226" t="n">
-        <v>-0.08004016235873</v>
+        <v>0.0774448083958757</v>
       </c>
       <c r="AC226" t="n">
-        <v>-0.801026054001779</v>
+        <v>-0.65483685823092</v>
       </c>
       <c r="AD226" t="n">
-        <v>-1.13324123532592</v>
+        <v>-0.987575156020119</v>
       </c>
       <c r="AE226" t="n">
-        <v>-1.23787386511485</v>
+        <v>-1.096259528873</v>
       </c>
     </row>
     <row r="227">
@@ -22639,31 +22639,31 @@
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.148176080593875</v>
+        <v>-0.148412638800071</v>
       </c>
       <c r="E227" t="n">
-        <v>-0.196815410962394</v>
+        <v>-0.197121935444428</v>
       </c>
       <c r="F227" t="n">
-        <v>-0.0316493515370918</v>
+        <v>-0.0435490481820444</v>
       </c>
       <c r="G227" t="n">
-        <v>-0.00246454783118823</v>
+        <v>-0.00635794315663765</v>
       </c>
       <c r="H227" t="n">
-        <v>-0.0262685201443142</v>
+        <v>-0.017004406632806</v>
       </c>
       <c r="I227" t="n">
-        <v>0.250909650231776</v>
+        <v>0.250917484302856</v>
       </c>
       <c r="J227" t="n">
-        <v>0.0102052032153379</v>
+        <v>0.00570573107974628</v>
       </c>
       <c r="K227" t="n">
-        <v>-0.148204655985602</v>
+        <v>-0.139294219496959</v>
       </c>
       <c r="L227" t="n">
-        <v>0.0110299332948583</v>
+        <v>0.0110303002117353</v>
       </c>
       <c r="M227" t="n">
         <v>0</v>
@@ -22675,52 +22675,52 @@
         <v>0</v>
       </c>
       <c r="P227" t="n">
-        <v>-0.00420754132495534</v>
+        <v>-0.00420768183636927</v>
       </c>
       <c r="Q227" t="n">
-        <v>-0.009602895581457</v>
+        <v>-0.00960321671191952</v>
       </c>
       <c r="R227" t="n">
-        <v>-0.00225344359409787</v>
+        <v>-0.00225351881071096</v>
       </c>
       <c r="S227" t="n">
-        <v>-0.00989329786880516</v>
+        <v>-0.00989362873505975</v>
       </c>
       <c r="T227" t="n">
-        <v>-0.00650308683627869</v>
+        <v>-0.00650330413466861</v>
       </c>
       <c r="U227" t="n">
-        <v>-0.000193143032293777</v>
+        <v>-0.000193149475813396</v>
       </c>
       <c r="V227" t="n">
-        <v>-0.000338962927136702</v>
+        <v>-0.000338974235763301</v>
       </c>
       <c r="W227" t="n">
-        <v>0.101254247651087</v>
+        <v>0.103369363798808</v>
       </c>
       <c r="X227" t="n">
-        <v>0.0255395385953897</v>
+        <v>0.0260908592101928</v>
       </c>
       <c r="Y227" t="n">
-        <v>-0.233413041022905</v>
+        <v>-0.23365221471876</v>
       </c>
       <c r="Z227" t="n">
-        <v>-0.111578450533364</v>
+        <v>-0.111882359525739</v>
       </c>
       <c r="AA227" t="n">
-        <v>0.200861671984785</v>
+        <v>0.189866470281682</v>
       </c>
       <c r="AB227" t="n">
-        <v>-0.043207704329037</v>
+        <v>-0.0316378100075418</v>
       </c>
       <c r="AC227" t="n">
-        <v>0.157745647534242</v>
+        <v>0.158292216096648</v>
       </c>
       <c r="AD227" t="n">
-        <v>-0.187245844022027</v>
+        <v>-0.187242358147851</v>
       </c>
       <c r="AE227" t="n">
-        <v>-0.932377977258624</v>
+        <v>-0.821769230465503</v>
       </c>
     </row>
     <row r="228">
@@ -22734,31 +22734,31 @@
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>-0.140458110675687</v>
+        <v>-0.140682347398469</v>
       </c>
       <c r="E228" t="n">
-        <v>-0.186656607064026</v>
+        <v>-0.186947310010096</v>
       </c>
       <c r="F228" t="n">
-        <v>0.0192152305972871</v>
+        <v>-0.00698425886088748</v>
       </c>
       <c r="G228" t="n">
-        <v>0.0115463661677605</v>
+        <v>0.00770870510059836</v>
       </c>
       <c r="H228" t="n">
-        <v>-0.0142621342632869</v>
+        <v>-0.00528041540948872</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0775549455812676</v>
+        <v>0.0775574813202917</v>
       </c>
       <c r="J228" t="n">
-        <v>0.0115958243126673</v>
+        <v>0.00720900216360417</v>
       </c>
       <c r="K228" t="n">
-        <v>-0.14318215702575</v>
+        <v>-0.134494603756346</v>
       </c>
       <c r="L228" t="n">
-        <v>0.0112120756904849</v>
+        <v>0.0112124486433643</v>
       </c>
       <c r="M228" t="n">
         <v>0</v>
@@ -22770,52 +22770,52 @@
         <v>0</v>
       </c>
       <c r="P228" t="n">
-        <v>-0.0045468213976324</v>
+        <v>-0.00454697325336154</v>
       </c>
       <c r="Q228" t="n">
-        <v>-0.00856922869056203</v>
+        <v>-0.00856951518219545</v>
       </c>
       <c r="R228" t="n">
-        <v>-0.00284364538533026</v>
+        <v>-0.00284374031659713</v>
       </c>
       <c r="S228" t="n">
-        <v>-0.00674665259466722</v>
+        <v>-0.00674687804768323</v>
       </c>
       <c r="T228" t="n">
-        <v>-0.00580085321925378</v>
+        <v>-0.00580104701958993</v>
       </c>
       <c r="U228" t="n">
-        <v>-0.00730976693763167</v>
+        <v>-0.0073100112434932</v>
       </c>
       <c r="V228" t="n">
-        <v>-0.000331070806111336</v>
+        <v>-0.000331081851304551</v>
       </c>
       <c r="W228" t="n">
-        <v>0.101056297598154</v>
+        <v>0.102809927659501</v>
       </c>
       <c r="X228" t="n">
-        <v>0.0255357258330154</v>
+        <v>0.0260708930959828</v>
       </c>
       <c r="Y228" t="n">
-        <v>-0.175014481420945</v>
+        <v>-0.175239867496321</v>
       </c>
       <c r="Z228" t="n">
-        <v>-0.152100236318768</v>
+        <v>-0.152389789912244</v>
       </c>
       <c r="AA228" t="n">
-        <v>0.10562736307484</v>
+        <v>0.0802092875406697</v>
       </c>
       <c r="AB228" t="n">
-        <v>-0.0413668316596409</v>
+        <v>-0.0303976356022582</v>
       </c>
       <c r="AC228" t="n">
-        <v>0.064306930317195</v>
+        <v>0.0498375827844027</v>
       </c>
       <c r="AD228" t="n">
-        <v>-0.262807787422518</v>
+        <v>-0.277792074624162</v>
       </c>
       <c r="AE228" t="n">
-        <v>-0.70926769125628</v>
+        <v>-0.637338468856781</v>
       </c>
     </row>
     <row r="229">
@@ -22829,31 +22829,31 @@
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>-0.158713894057266</v>
+        <v>-0.158967275533724</v>
       </c>
       <c r="E229" t="n">
-        <v>-0.197409852541738</v>
+        <v>-0.197717302819656</v>
       </c>
       <c r="F229" t="n">
-        <v>0.0408056034098479</v>
+        <v>0.0292143834952303</v>
       </c>
       <c r="G229" t="n">
-        <v>0.026816932333981</v>
+        <v>0.0230080626617174</v>
       </c>
       <c r="H229" t="n">
-        <v>-0.00673602062284839</v>
+        <v>0.00202867259195626</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0530514800304113</v>
+        <v>-0.0530532737872542</v>
       </c>
       <c r="J229" t="n">
-        <v>0.0118291883531254</v>
+        <v>0.00751378843311881</v>
       </c>
       <c r="K229" t="n">
-        <v>-0.0931421042058728</v>
+        <v>-0.084626419826619</v>
       </c>
       <c r="L229" t="n">
-        <v>0.0113464439039722</v>
+        <v>0.0113468213160447</v>
       </c>
       <c r="M229" t="n">
         <v>0</v>
@@ -22865,52 +22865,52 @@
         <v>0</v>
       </c>
       <c r="P229" t="n">
-        <v>-0.00467887355826014</v>
+        <v>-0.00467902982911738</v>
       </c>
       <c r="Q229" t="n">
-        <v>-0.00672162807762801</v>
+        <v>-0.00672185269204388</v>
       </c>
       <c r="R229" t="n">
-        <v>-0.000299259742740938</v>
+        <v>-0.000299269726551683</v>
       </c>
       <c r="S229" t="n">
-        <v>-0.00308262761955826</v>
+        <v>-0.00308273053499964</v>
       </c>
       <c r="T229" t="n">
-        <v>-0.00322440498551158</v>
+        <v>-0.00322451263820183</v>
       </c>
       <c r="U229" t="n">
-        <v>-0.00617786832708786</v>
+        <v>-0.00617807474218577</v>
       </c>
       <c r="V229" t="n">
-        <v>-0.000325681797821561</v>
+        <v>-0.000325692663239272</v>
       </c>
       <c r="W229" t="n">
-        <v>0.102110179847018</v>
+        <v>0.103936860427178</v>
       </c>
       <c r="X229" t="n">
-        <v>0.0225274192483949</v>
+        <v>0.0230958713548606</v>
       </c>
       <c r="Y229" t="n">
-        <v>-0.218269008593826</v>
+        <v>-0.218524309635668</v>
       </c>
       <c r="Z229" t="n">
-        <v>-0.137854738005178</v>
+        <v>-0.138160268717712</v>
       </c>
       <c r="AA229" t="n">
-        <v>0.0196906792830349</v>
+        <v>0.00873380891502822</v>
       </c>
       <c r="AB229" t="n">
-        <v>0.0184349975660201</v>
+        <v>0.0293368892335976</v>
       </c>
       <c r="AC229" t="n">
-        <v>0.0381218319390021</v>
+        <v>0.038067979929672</v>
       </c>
       <c r="AD229" t="n">
-        <v>-0.318001914660002</v>
+        <v>-0.318616598423708</v>
       </c>
       <c r="AE229" t="n">
-        <v>-0.475324195357617</v>
+        <v>-0.442806546803961</v>
       </c>
     </row>
     <row r="230">
@@ -22924,31 +22924,31 @@
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>-0.153429928954711</v>
+        <v>-0.153674874755848</v>
       </c>
       <c r="E230" t="n">
-        <v>-0.201617406053679</v>
+        <v>-0.201931409264391</v>
       </c>
       <c r="F230" t="n">
-        <v>-0.115802938063154</v>
+        <v>-0.119790627104167</v>
       </c>
       <c r="G230" t="n">
-        <v>0.0213093881136288</v>
+        <v>0.0212961248217644</v>
       </c>
       <c r="H230" t="n">
-        <v>-0.00716528068522892</v>
+        <v>0.00137878084953047</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.20156527298399</v>
+        <v>-0.20157234261226</v>
       </c>
       <c r="J230" t="n">
-        <v>0.0132699261485339</v>
+        <v>0.00904353396654501</v>
       </c>
       <c r="K230" t="n">
-        <v>-0.0829243302216015</v>
+        <v>-0.0743219026180051</v>
       </c>
       <c r="L230" t="n">
-        <v>0.0116379107339146</v>
+        <v>0.0116382978137369</v>
       </c>
       <c r="M230" t="n">
         <v>0</v>
@@ -22960,52 +22960,52 @@
         <v>0</v>
       </c>
       <c r="P230" t="n">
-        <v>-0.00187667017415156</v>
+        <v>-0.0018767328086848</v>
       </c>
       <c r="Q230" t="n">
-        <v>-0.00601918796692486</v>
+        <v>-0.00601938907163265</v>
       </c>
       <c r="R230" t="n">
-        <v>-0.000293788370115892</v>
+        <v>-0.000293798171445692</v>
       </c>
       <c r="S230" t="n">
-        <v>-0.00137638007960116</v>
+        <v>-0.00137642601087763</v>
       </c>
       <c r="T230" t="n">
-        <v>-0.00182323178334611</v>
+        <v>-0.00182329263351616</v>
       </c>
       <c r="U230" t="n">
-        <v>-0.00573074329281721</v>
+        <v>-0.00573093474635067</v>
       </c>
       <c r="V230" t="n">
-        <v>-0.000319798530206102</v>
+        <v>-0.000319809199413898</v>
       </c>
       <c r="W230" t="n">
-        <v>0.109993952471134</v>
+        <v>0.112066574886822</v>
       </c>
       <c r="X230" t="n">
-        <v>0.0140933530840579</v>
+        <v>0.0145555242024876</v>
       </c>
       <c r="Y230" t="n">
-        <v>-0.198847482614133</v>
+        <v>-0.199093925560418</v>
       </c>
       <c r="Z230" t="n">
-        <v>-0.156199852394257</v>
+        <v>-0.156512358459821</v>
       </c>
       <c r="AA230" t="n">
-        <v>-0.290109225880273</v>
+        <v>-0.289794640309969</v>
       </c>
       <c r="AB230" t="n">
-        <v>0.0354569827882036</v>
+        <v>0.0465846765244593</v>
       </c>
       <c r="AC230" t="n">
-        <v>-0.254543509473806</v>
+        <v>-0.243067032690607</v>
       </c>
       <c r="AD230" t="n">
-        <v>-0.609590844482197</v>
+        <v>-0.598673316710846</v>
       </c>
       <c r="AE230" t="n">
-        <v>-0.344411597646687</v>
+        <v>-0.345581086976642</v>
       </c>
     </row>
     <row r="231">
@@ -23019,31 +23019,31 @@
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>-6.274071451743</v>
+        <v>-6.28408779906587</v>
       </c>
       <c r="E231" t="n">
-        <v>-10.8910610556931</v>
+        <v>-10.9080230244362</v>
       </c>
       <c r="F231" t="n">
-        <v>7.34462093874844</v>
+        <v>7.41110456463305</v>
       </c>
       <c r="G231" t="n">
-        <v>4.12800336972667</v>
+        <v>4.1358390035692</v>
       </c>
       <c r="H231" t="n">
-        <v>0.236457225619537</v>
+        <v>0.235587753402985</v>
       </c>
       <c r="I231" t="n">
-        <v>-1.8924367603721</v>
+        <v>-1.89253018357234</v>
       </c>
       <c r="J231" t="n">
-        <v>0.0777088115177268</v>
+        <v>0.0781427550492037</v>
       </c>
       <c r="K231" t="n">
-        <v>-7.07886236896997</v>
+        <v>-7.14722460947297</v>
       </c>
       <c r="L231" t="n">
-        <v>-0.731294333074805</v>
+        <v>-0.731323282816941</v>
       </c>
       <c r="M231" t="n">
         <v>0</v>
@@ -23055,52 +23055,52 @@
         <v>0</v>
       </c>
       <c r="P231" t="n">
-        <v>-0.09517191160616</v>
+        <v>-0.0951751639028847</v>
       </c>
       <c r="Q231" t="n">
-        <v>-0.0671403188695422</v>
+        <v>-0.0671425971654246</v>
       </c>
       <c r="R231" t="n">
-        <v>-0.000287034788668414</v>
+        <v>-0.000287044364671847</v>
       </c>
       <c r="S231" t="n">
-        <v>-0.0010388462452094</v>
+        <v>-0.00103888090965514</v>
       </c>
       <c r="T231" t="n">
-        <v>-0.001533369339043</v>
+        <v>-0.00153342051134481</v>
       </c>
       <c r="U231" t="n">
-        <v>-0.00527097082071952</v>
+        <v>-0.00527114689451538</v>
       </c>
       <c r="V231" t="n">
-        <v>-0.000252684320366087</v>
+        <v>-0.000252692750315485</v>
       </c>
       <c r="W231" t="n">
-        <v>-5.94921587386904</v>
+        <v>-6.07690959991829</v>
       </c>
       <c r="X231" t="n">
-        <v>-0.987626071168798</v>
+        <v>-1.02112545164236</v>
       </c>
       <c r="Y231" t="n">
-        <v>-7.87813385913275</v>
+        <v>-7.88820371694072</v>
       </c>
       <c r="Z231" t="n">
-        <v>-9.28699864830338</v>
+        <v>-9.30390710656139</v>
       </c>
       <c r="AA231" t="n">
-        <v>9.76118043628316</v>
+        <v>9.83237406920548</v>
       </c>
       <c r="AB231" t="n">
-        <v>-15.6307820585151</v>
+        <v>-15.8842014232208</v>
       </c>
       <c r="AC231" t="n">
-        <v>-4.25959595984037</v>
+        <v>-4.40157013486307</v>
       </c>
       <c r="AD231" t="n">
-        <v>-21.4247284672765</v>
+        <v>-21.5936809583652</v>
       </c>
       <c r="AE231" t="n">
-        <v>-5.65378225346031</v>
+        <v>-5.69719073703097</v>
       </c>
     </row>
     <row r="232">
@@ -23120,25 +23120,25 @@
         <v>#NUM!</v>
       </c>
       <c r="F232" t="n">
-        <v>7.34028150817136</v>
+        <v>7.40667181094843</v>
       </c>
       <c r="G232" t="n">
-        <v>4.08873467508956</v>
+        <v>4.09650477877435</v>
       </c>
       <c r="H232" t="n">
-        <v>0.23186340611593</v>
+        <v>0.231006555118409</v>
       </c>
       <c r="I232" t="n">
         <v>0</v>
       </c>
       <c r="J232" t="n">
-        <v>0.0756499339818701</v>
+        <v>0.076077524851577</v>
       </c>
       <c r="K232" t="n">
-        <v>-6.96087894939922</v>
+        <v>-7.02784532339994</v>
       </c>
       <c r="L232" t="n">
-        <v>-0.727317573570917</v>
+        <v>-0.72734634588118</v>
       </c>
       <c r="M232" t="n">
         <v>0</v>
@@ -23150,31 +23150,31 @@
         <v>0</v>
       </c>
       <c r="P232" t="n">
-        <v>-0.0796345638301537</v>
+        <v>-0.0796372746545218</v>
       </c>
       <c r="Q232" t="n">
-        <v>-0.0572826051079501</v>
+        <v>-0.057284544100989</v>
       </c>
       <c r="R232" t="n">
-        <v>-0.00028140051601946</v>
+        <v>-0.000281409904046855</v>
       </c>
       <c r="S232" t="n">
-        <v>-0.00102290236554089</v>
+        <v>-0.00102293649787806</v>
       </c>
       <c r="T232" t="n">
-        <v>-0.00126747679254835</v>
+        <v>-0.00126751908850159</v>
       </c>
       <c r="U232" t="n">
-        <v>-0.00313779649383815</v>
+        <v>-0.00313790125300507</v>
       </c>
       <c r="V232" t="n">
-        <v>-0.000247819501253074</v>
+        <v>-0.000247827768865982</v>
       </c>
       <c r="W232" t="n">
-        <v>-5.9201262624243</v>
+        <v>-6.04711138603007</v>
       </c>
       <c r="X232" t="n">
-        <v>-0.984180781257747</v>
+        <v>-1.01746836951814</v>
       </c>
       <c r="Y232" t="e">
         <v>#NUM!</v>
@@ -23183,19 +23183,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA232" t="n">
-        <v>11.3734803571734</v>
+        <v>11.44281620329</v>
       </c>
       <c r="AB232" t="n">
-        <v>-15.4313263355816</v>
+        <v>-15.6818962663538</v>
       </c>
       <c r="AC232" t="n">
-        <v>-2.19718206661957</v>
+        <v>-2.33409653438257</v>
       </c>
       <c r="AD232" t="n">
         <v>0</v>
       </c>
       <c r="AE232" t="n">
-        <v>-5.58808030660468</v>
+        <v>-5.62774271837493</v>
       </c>
     </row>
     <row r="233">
@@ -23215,25 +23215,25 @@
         <v>#NUM!</v>
       </c>
       <c r="F233" t="n">
-        <v>3.6708826915257</v>
+        <v>3.71175479669329</v>
       </c>
       <c r="G233" t="n">
-        <v>2.05618530384956</v>
+        <v>2.06016853851676</v>
       </c>
       <c r="H233" t="n">
-        <v>0.235749920235205</v>
+        <v>0.234903645498139</v>
       </c>
       <c r="I233" t="n">
         <v>0</v>
       </c>
       <c r="J233" t="n">
-        <v>0.0750093114979357</v>
+        <v>0.075431754655377</v>
       </c>
       <c r="K233" t="n">
-        <v>-6.85652855082813</v>
+        <v>-6.9222373427167</v>
       </c>
       <c r="L233" t="n">
-        <v>-0.724691567503867</v>
+        <v>-0.724720214539653</v>
       </c>
       <c r="M233" t="n">
         <v>0</v>
@@ -23245,31 +23245,31 @@
         <v>0</v>
       </c>
       <c r="P233" t="n">
-        <v>-0.073784284093115</v>
+        <v>-0.0737867920223461</v>
       </c>
       <c r="Q233" t="n">
-        <v>-0.0535980979947818</v>
+        <v>-0.05359991055025</v>
       </c>
       <c r="R233" t="n">
-        <v>0.000203337487574231</v>
+        <v>0.000203344270475837</v>
       </c>
       <c r="S233" t="n">
-        <v>-0.00101836074443453</v>
+        <v>-0.00101839472511128</v>
       </c>
       <c r="T233" t="n">
-        <v>-0.000246581090156494</v>
+        <v>-0.000246589316465441</v>
       </c>
       <c r="U233" t="n">
-        <v>-0.00174097972355573</v>
+        <v>-0.00174103782739379</v>
       </c>
       <c r="V233" t="n">
-        <v>-0.000243462051132119</v>
+        <v>-0.000243470173402295</v>
       </c>
       <c r="W233" t="n">
-        <v>-5.89894216558565</v>
+        <v>-6.02546739748083</v>
       </c>
       <c r="X233" t="n">
-        <v>-0.982064579620993</v>
+        <v>-1.01526155499267</v>
       </c>
       <c r="Y233" t="e">
         <v>#NUM!</v>
@@ -23278,19 +23278,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA233" t="n">
-        <v>5.93782550074302</v>
+        <v>5.98090712999536</v>
       </c>
       <c r="AB233" t="n">
-        <v>-15.2747728814194</v>
+        <v>-15.5230916187226</v>
       </c>
       <c r="AC233" t="n">
-        <v>-8.38689428832716</v>
+        <v>-8.56844634435761</v>
       </c>
       <c r="AD233" t="n">
         <v>0</v>
       </c>
       <c r="AE233" t="n">
-        <v>-5.50857982793968</v>
+        <v>-5.54808856876901</v>
       </c>
     </row>
     <row r="234">
@@ -23310,25 +23310,25 @@
         <v>#NUM!</v>
       </c>
       <c r="F234" t="n">
-        <v>3.66858958296049</v>
+        <v>3.69578716675083</v>
       </c>
       <c r="G234" t="n">
-        <v>2.03695832437417</v>
+        <v>2.04091025606204</v>
       </c>
       <c r="H234" t="n">
-        <v>0.238435834340507</v>
+        <v>0.228872207222348</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
       </c>
       <c r="J234" t="n">
-        <v>0.0717501713744041</v>
+        <v>0.0768299889348334</v>
       </c>
       <c r="K234" t="n">
-        <v>-6.8659067720727</v>
+        <v>-6.94196716959226</v>
       </c>
       <c r="L234" t="n">
-        <v>-0.721658234892513</v>
+        <v>-0.72168673976959</v>
       </c>
       <c r="M234" t="n">
         <v>0</v>
@@ -23340,31 +23340,31 @@
         <v>0</v>
       </c>
       <c r="P234" t="n">
-        <v>-0.0686392515126324</v>
+        <v>-0.0686415815111592</v>
       </c>
       <c r="Q234" t="n">
-        <v>-0.0518759739481879</v>
+        <v>-0.051877727483063</v>
       </c>
       <c r="R234" t="n">
-        <v>0.000199642788734045</v>
+        <v>0.000199649448274403</v>
       </c>
       <c r="S234" t="n">
-        <v>-0.00102315510325043</v>
+        <v>-0.00102318924398752</v>
       </c>
       <c r="T234" t="n">
         <v>0</v>
       </c>
       <c r="U234" t="n">
-        <v>-0.00170906507897664</v>
+        <v>-0.00170912211727086</v>
       </c>
       <c r="V234" t="n">
-        <v>-0.000239005086281634</v>
+        <v>-0.000239013059864166</v>
       </c>
       <c r="W234" t="n">
-        <v>-5.87498644273963</v>
+        <v>-6.00097918708418</v>
       </c>
       <c r="X234" t="n">
-        <v>-0.978859425048632</v>
+        <v>-1.01194795128205</v>
       </c>
       <c r="Y234" t="e">
         <v>#NUM!</v>
@@ -23373,19 +23373,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA234" t="n">
-        <v>5.91673629831376</v>
+        <v>5.94265399183359</v>
       </c>
       <c r="AB234" t="n">
-        <v>-15.2427928632324</v>
+        <v>-15.501538155925</v>
       </c>
       <c r="AC234" t="n">
-        <v>-8.38213435272095</v>
+        <v>-8.59355742070488</v>
       </c>
       <c r="AD234" t="n">
         <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>-5.35618211681913</v>
+        <v>-5.39842023959129</v>
       </c>
     </row>
     <row r="235">
@@ -23405,19 +23405,19 @@
         <v>#NUM!</v>
       </c>
       <c r="F235" t="n">
-        <v>3.62091042000776</v>
+        <v>3.64777626455809</v>
       </c>
       <c r="G235" t="n">
-        <v>2.0156200934611</v>
+        <v>2.01953424170871</v>
       </c>
       <c r="H235" t="n">
-        <v>0.240909898011587</v>
+        <v>0.231247165562742</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>0.0703346472827135</v>
+        <v>0.0750911176556549</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
@@ -23435,25 +23435,25 @@
         <v>0</v>
       </c>
       <c r="P235" t="n">
-        <v>-0.0408265729089207</v>
+        <v>-0.0408279491088684</v>
       </c>
       <c r="Q235" t="n">
-        <v>-0.0435382304705362</v>
+        <v>-0.0435396990855192</v>
       </c>
       <c r="R235" t="n">
-        <v>0.000195724705252448</v>
+        <v>0.000195731234193339</v>
       </c>
       <c r="S235" t="n">
-        <v>-0.000603596119345425</v>
+        <v>-0.000603616258038131</v>
       </c>
       <c r="T235" t="n">
         <v>0</v>
       </c>
       <c r="U235" t="n">
-        <v>-0.00134276547416713</v>
+        <v>-0.00134281028332211</v>
       </c>
       <c r="V235" t="n">
-        <v>-0.0000801973653759384</v>
+        <v>-0.0000802000407151782</v>
       </c>
       <c r="W235" t="n">
         <v>0</v>
@@ -23468,19 +23468,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA235" t="n">
-        <v>5.85072373816674</v>
+        <v>5.87589270373488</v>
       </c>
       <c r="AB235" t="n">
-        <v>-0.0862161623990945</v>
+        <v>-0.0862191020547883</v>
       </c>
       <c r="AC235" t="n">
-        <v>5.76992229095146</v>
+        <v>5.79512072270948</v>
       </c>
       <c r="AD235" t="n">
         <v>0</v>
       </c>
       <c r="AE235" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="236">
@@ -23500,19 +23500,19 @@
         <v>#NUM!</v>
       </c>
       <c r="F236" t="n">
-        <v>3.58111891062191</v>
+        <v>3.60771077107197</v>
       </c>
       <c r="G236" t="n">
-        <v>1.99679219968312</v>
+        <v>2.00067564448385</v>
       </c>
       <c r="H236" t="n">
-        <v>0.243944876323294</v>
+        <v>0.234160542051547</v>
       </c>
       <c r="I236" t="n">
         <v>0</v>
       </c>
       <c r="J236" t="n">
-        <v>0.0691563640307958</v>
+        <v>0.0738331863055758</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -23530,16 +23530,16 @@
         <v>0</v>
       </c>
       <c r="P236" t="n">
-        <v>-0.0222835620506624</v>
+        <v>-0.0222843096559488</v>
       </c>
       <c r="Q236" t="n">
-        <v>-0.042600410299256</v>
+        <v>-0.042601846915859</v>
       </c>
       <c r="R236" t="n">
-        <v>0.000192253031801122</v>
+        <v>0.000192259444913168</v>
       </c>
       <c r="S236" t="n">
-        <v>-0.000602092031745545</v>
+        <v>-0.000602112120240131</v>
       </c>
       <c r="T236" t="n">
         <v>0</v>
@@ -23548,7 +23548,7 @@
         <v>0</v>
       </c>
       <c r="V236" t="n">
-        <v>-0.0000787731404831886</v>
+        <v>-0.0000787757684384681</v>
       </c>
       <c r="W236" t="n">
         <v>0</v>
@@ -23563,19 +23563,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA236" t="n">
-        <v>5.79577698211446</v>
+        <v>5.82046744126944</v>
       </c>
       <c r="AB236" t="n">
-        <v>-0.0653829873247719</v>
+        <v>-0.0653852049528357</v>
       </c>
       <c r="AC236" t="n">
-        <v>5.73445546045961</v>
+        <v>5.75916783355295</v>
       </c>
       <c r="AD236" t="n">
         <v>0</v>
       </c>
       <c r="AE236" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="237">
@@ -23595,19 +23595,19 @@
         <v>#NUM!</v>
       </c>
       <c r="F237" t="n">
-        <v>3.53799665616851</v>
+        <v>3.56428880655508</v>
       </c>
       <c r="G237" t="n">
-        <v>1.97724359079628</v>
+        <v>1.98109242658752</v>
       </c>
       <c r="H237" t="n">
-        <v>0.237988386504441</v>
+        <v>0.228442675489121</v>
       </c>
       <c r="I237" t="n">
         <v>0</v>
       </c>
       <c r="J237" t="n">
-        <v>0.0678300560897688</v>
+        <v>0.07241722053566</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -23625,16 +23625,16 @@
         <v>0</v>
       </c>
       <c r="P237" t="n">
-        <v>-0.0219825135519265</v>
+        <v>-0.021983250998931</v>
       </c>
       <c r="Q237" t="n">
-        <v>-0.0428944730015343</v>
+        <v>-0.0428959196358591</v>
       </c>
       <c r="R237" t="n">
-        <v>0.000443899103206305</v>
+        <v>0.000443913909670966</v>
       </c>
       <c r="S237" t="n">
-        <v>-0.000602299932441667</v>
+        <v>-0.000602320027817012</v>
       </c>
       <c r="T237" t="n">
         <v>0</v>
@@ -23643,7 +23643,7 @@
         <v>0</v>
       </c>
       <c r="V237" t="n">
-        <v>-0.0000772846115611024</v>
+        <v>-0.0000772871897951424</v>
       </c>
       <c r="W237" t="n">
         <v>0</v>
@@ -23658,19 +23658,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA237" t="n">
-        <v>5.72817338972697</v>
+        <v>5.7526892005781</v>
       </c>
       <c r="AB237" t="n">
-        <v>-0.0651228271892532</v>
+        <v>-0.0651250358335227</v>
       </c>
       <c r="AC237" t="n">
-        <v>5.66704647564438</v>
+        <v>5.69158389670264</v>
       </c>
       <c r="AD237" t="n">
         <v>0</v>
       </c>
       <c r="AE237" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="238">
@@ -23690,19 +23690,19 @@
         <v>#NUM!</v>
       </c>
       <c r="F238" t="n">
-        <v>3.58938510041415</v>
+        <v>3.61616546284846</v>
       </c>
       <c r="G238" t="n">
-        <v>1.96015877864913</v>
+        <v>1.96397742721916</v>
       </c>
       <c r="H238" t="n">
-        <v>0.232317659002568</v>
+        <v>0.222999126370206</v>
       </c>
       <c r="I238" t="n">
         <v>0</v>
       </c>
       <c r="J238" t="n">
-        <v>0.06668120529485</v>
+        <v>0.0711907085392884</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -23720,16 +23720,16 @@
         <v>0</v>
       </c>
       <c r="P238" t="n">
-        <v>-0.017681184689841</v>
+        <v>-0.0176817771874647</v>
       </c>
       <c r="Q238" t="n">
-        <v>-0.0428710447541283</v>
+        <v>-0.0428724905681749</v>
       </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
       <c r="S238" t="n">
-        <v>-0.000503175320367836</v>
+        <v>-0.000503192108089618</v>
       </c>
       <c r="T238" t="n">
         <v>0</v>
@@ -23738,7 +23738,7 @@
         <v>0</v>
       </c>
       <c r="V238" t="n">
-        <v>-0.000075872672803126</v>
+        <v>-0.0000758752039149069</v>
       </c>
       <c r="W238" t="n">
         <v>0</v>
@@ -23753,19 +23753,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA238" t="n">
-        <v>5.75564511517377</v>
+        <v>5.78075649702727</v>
       </c>
       <c r="AB238" t="n">
-        <v>-0.0611396735798925</v>
+        <v>-0.0611417450140355</v>
       </c>
       <c r="AC238" t="n">
-        <v>5.69826991358212</v>
+        <v>5.72340198060486</v>
       </c>
       <c r="AD238" t="n">
         <v>0</v>
       </c>
       <c r="AE238" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="239">
@@ -23791,13 +23791,13 @@
         <v>0</v>
       </c>
       <c r="H239" t="n">
-        <v>0.226621156224318</v>
+        <v>0.217530854108107</v>
       </c>
       <c r="I239" t="n">
         <v>0</v>
       </c>
       <c r="J239" t="n">
-        <v>0.0655577993659203</v>
+        <v>0.0699913594698335</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -23818,13 +23818,13 @@
         <v>0</v>
       </c>
       <c r="Q239" t="n">
-        <v>-0.0333432560577646</v>
+        <v>-0.033344377834667</v>
       </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
       <c r="S239" t="n">
-        <v>-0.000397412352810383</v>
+        <v>-0.000397425611547924</v>
       </c>
       <c r="T239" t="n">
         <v>0</v>
@@ -23848,19 +23848,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA239" t="n">
-        <v>0.292021714970504</v>
+        <v>0.287360819989515</v>
       </c>
       <c r="AB239" t="n">
-        <v>-0.0337408085755119</v>
+        <v>-0.0337419438416393</v>
       </c>
       <c r="AC239" t="n">
-        <v>0.258385182497859</v>
+        <v>0.253721652411467</v>
       </c>
       <c r="AD239" t="n">
         <v>0</v>
       </c>
       <c r="AE239" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="240">
@@ -23886,13 +23886,13 @@
         <v>0</v>
       </c>
       <c r="H240" t="n">
-        <v>0.220801540025901</v>
+        <v>0.211944427507829</v>
       </c>
       <c r="I240" t="n">
         <v>0</v>
       </c>
       <c r="J240" t="n">
-        <v>0.0641960707994223</v>
+        <v>0.068537573143719</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
@@ -23913,13 +23913,13 @@
         <v>0</v>
       </c>
       <c r="Q240" t="n">
-        <v>-0.0326832421285955</v>
+        <v>-0.0326843415206378</v>
       </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
       <c r="S240" t="n">
-        <v>-0.000294186370964438</v>
+        <v>-0.000294196185575559</v>
       </c>
       <c r="T240" t="n">
         <v>0</v>
@@ -23943,19 +23943,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA240" t="n">
-        <v>0.284847529496917</v>
+        <v>0.280327955512739</v>
       </c>
       <c r="AB240" t="n">
-        <v>-0.0329775302462111</v>
+        <v>-0.0329786396201192</v>
       </c>
       <c r="AC240" t="n">
-        <v>0.251969453078873</v>
+        <v>0.247447348641465</v>
       </c>
       <c r="AD240" t="n">
         <v>0</v>
       </c>
       <c r="AE240" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="241">
@@ -23981,13 +23981,13 @@
         <v>0</v>
       </c>
       <c r="H241" t="n">
-        <v>0.215294406874647</v>
+        <v>0.206657967916124</v>
       </c>
       <c r="I241" t="n">
         <v>0</v>
       </c>
       <c r="J241" t="n">
-        <v>0.0630496274239362</v>
+        <v>0.0673136260870223</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -24008,13 +24008,13 @@
         <v>0</v>
       </c>
       <c r="Q241" t="n">
-        <v>-0.0325155938204141</v>
+        <v>-0.0325166875234577</v>
       </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
       <c r="S241" t="n">
-        <v>-0.00019413281453202</v>
+        <v>-0.00019413929093192</v>
       </c>
       <c r="T241" t="n">
         <v>0</v>
@@ -24038,19 +24038,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA241" t="n">
-        <v>0.278200362781694</v>
+        <v>0.273824128036082</v>
       </c>
       <c r="AB241" t="n">
-        <v>-0.0327097934089944</v>
+        <v>-0.0327108936982566</v>
       </c>
       <c r="AC241" t="n">
-        <v>0.24558687815917</v>
+        <v>0.241208180137775</v>
       </c>
       <c r="AD241" t="n">
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="242">
@@ -24076,13 +24076,13 @@
         <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>0.210070746582606</v>
+        <v>0.201643624847002</v>
       </c>
       <c r="I242" t="n">
         <v>0</v>
       </c>
       <c r="J242" t="n">
-        <v>0.0617800942131593</v>
+        <v>0.0659582680602653</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
@@ -24103,13 +24103,13 @@
         <v>0</v>
       </c>
       <c r="Q242" t="n">
-        <v>-0.0317000555575629</v>
+        <v>-0.0317011215972536</v>
       </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
       <c r="S242" t="n">
-        <v>-0.0000969420193047341</v>
+        <v>-0.0000969452533365511</v>
       </c>
       <c r="T242" t="n">
         <v>0</v>
@@ -24133,19 +24133,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA242" t="n">
-        <v>0.27171366526641</v>
+        <v>0.267461094550151</v>
       </c>
       <c r="AB242" t="n">
-        <v>-0.0317970300408741</v>
+        <v>-0.0317980993679673</v>
       </c>
       <c r="AC242" t="n">
-        <v>0.24000794899665</v>
+        <v>0.23575302395497</v>
       </c>
       <c r="AD242" t="n">
         <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="243">
@@ -24198,7 +24198,7 @@
         <v>0</v>
       </c>
       <c r="Q243" t="n">
-        <v>-0.0106469776121809</v>
+        <v>-0.0106473337503971</v>
       </c>
       <c r="R243" t="n">
         <v>0</v>
@@ -24231,16 +24231,16 @@
         <v>0</v>
       </c>
       <c r="AB243" t="n">
-        <v>-0.0106469776121809</v>
+        <v>-0.0106473337503971</v>
       </c>
       <c r="AC243" t="n">
-        <v>-0.0106469776121809</v>
+        <v>-0.0106473337503971</v>
       </c>
       <c r="AD243" t="n">
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="244">
@@ -24293,7 +24293,7 @@
         <v>0</v>
       </c>
       <c r="Q244" t="n">
-        <v>-0.0104376399051294</v>
+        <v>-0.0104379890224626</v>
       </c>
       <c r="R244" t="n">
         <v>0</v>
@@ -24326,16 +24326,16 @@
         <v>0</v>
       </c>
       <c r="AB244" t="n">
-        <v>-0.0104376399051294</v>
+        <v>-0.0104379890224626</v>
       </c>
       <c r="AC244" t="n">
-        <v>-0.0104376399051294</v>
+        <v>-0.0104379890224626</v>
       </c>
       <c r="AD244" t="n">
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="245">
@@ -24388,7 +24388,7 @@
         <v>0</v>
       </c>
       <c r="Q245" t="n">
-        <v>-0.010247330369453</v>
+        <v>-0.0102476731033623</v>
       </c>
       <c r="R245" t="n">
         <v>0</v>
@@ -24421,16 +24421,16 @@
         <v>0</v>
       </c>
       <c r="AB245" t="n">
-        <v>-0.010247330369453</v>
+        <v>-0.0102476731033623</v>
       </c>
       <c r="AC245" t="n">
-        <v>-0.010247330369453</v>
+        <v>-0.0102476731033623</v>
       </c>
       <c r="AD245" t="n">
         <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="246">
@@ -24483,7 +24483,7 @@
         <v>0</v>
       </c>
       <c r="Q246" t="n">
-        <v>-0.0100516476860069</v>
+        <v>-0.010051983857906</v>
       </c>
       <c r="R246" t="n">
         <v>0</v>
@@ -24516,16 +24516,16 @@
         <v>0</v>
       </c>
       <c r="AB246" t="n">
-        <v>-0.0100516476860069</v>
+        <v>-0.010051983857906</v>
       </c>
       <c r="AC246" t="n">
-        <v>-0.0100516476860069</v>
+        <v>-0.010051983857906</v>
       </c>
       <c r="AD246" t="n">
         <v>0</v>
       </c>
       <c r="AE246" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="247">
@@ -24620,7 +24620,7 @@
         <v>0</v>
       </c>
       <c r="AE247" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="248">
@@ -24715,7 +24715,7 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="249">
@@ -24810,7 +24810,7 @@
         <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="250">
@@ -24905,7 +24905,7 @@
         <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="251">
@@ -25000,7 +25000,7 @@
         <v>0</v>
       </c>
       <c r="AE251" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="252">
@@ -25095,7 +25095,7 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="253">
@@ -25190,7 +25190,7 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="254">
@@ -25285,7 +25285,7 @@
         <v>0</v>
       </c>
       <c r="AE254" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="255">
@@ -25380,7 +25380,7 @@
         <v>0</v>
       </c>
       <c r="AE255" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="256">
@@ -25475,7 +25475,7 @@
         <v>0</v>
       </c>
       <c r="AE256" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="257">
@@ -25570,7 +25570,7 @@
         <v>0</v>
       </c>
       <c r="AE257" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="258">
@@ -25665,7 +25665,7 @@
         <v>0</v>
       </c>
       <c r="AE258" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="259">
@@ -25760,7 +25760,7 @@
         <v>0</v>
       </c>
       <c r="AE259" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="260">
@@ -25855,7 +25855,7 @@
         <v>0</v>
       </c>
       <c r="AE260" t="n">
-        <v>-0.00000000000000177635683940025</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
   </sheetData>
